--- a/data/trans_camb/IP16A01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-33,59; -6,48</t>
+          <t>-35,43; -6,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-71,73; -29,63</t>
+          <t>-72,86; -30,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-80,57; -40,63</t>
+          <t>-80,46; -43,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-65,95; -27,96</t>
+          <t>-66,82; -27,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,79; -23,63</t>
+          <t>-62,08; -22,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-62,95; -26,85</t>
+          <t>-60,92; -26,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,75; -21,2</t>
+          <t>-47,24; -20,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-59,31; -30,83</t>
+          <t>-59,61; -31,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-70,67; -40,93</t>
+          <t>-69,19; -40,37</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,59; -6,48</t>
+          <t>-35,43; -6,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-71,73; -29,63</t>
+          <t>-72,86; -30,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-80,57; -40,63</t>
+          <t>-80,46; -43,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-65,95; -27,96</t>
+          <t>-66,82; -27,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,79; -23,63</t>
+          <t>-62,08; -22,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,95; -26,85</t>
+          <t>-60,92; -26,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,75; -21,2</t>
+          <t>-47,24; -20,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,31; -30,83</t>
+          <t>-59,61; -31,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-70,67; -40,93</t>
+          <t>-69,19; -40,37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-58,02; -26,01</t>
+          <t>-58,56; -26,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-43,55; -12,64</t>
+          <t>-41,82; -14,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-63,25; -10,8</t>
+          <t>-62,11; -9,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-55,6; -24,62</t>
+          <t>-55,09; -23,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-67,53; -31,83</t>
+          <t>-66,4; -32,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,95; -32,02</t>
+          <t>-57,12; -32,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,07; -29,01</t>
+          <t>-51,64; -29,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,96; -25,8</t>
+          <t>-47,76; -24,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-52,9; -18,31</t>
+          <t>-53,05; -17,17</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,02; -26,01</t>
+          <t>-58,56; -26,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,55; -12,64</t>
+          <t>-41,82; -14,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,25; -10,8</t>
+          <t>-62,11; -9,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,6; -24,62</t>
+          <t>-55,09; -23,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,53; -31,83</t>
+          <t>-66,4; -32,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,95; -32,02</t>
+          <t>-57,12; -32,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,07; -29,01</t>
+          <t>-51,64; -29,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,96; -25,8</t>
+          <t>-47,76; -24,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,9; -18,31</t>
+          <t>-53,05; -17,17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-52,89; -10,38</t>
+          <t>-53,01; -13,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-76,84; -23,58</t>
+          <t>-76,86; -22,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-45,76; -13,17</t>
+          <t>-47,81; -13,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-37,03; -6,83</t>
+          <t>-37,75; -8,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,73; -17,08</t>
+          <t>-68,41; -16,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-48,06; -13,7</t>
+          <t>-45,43; -10,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,9; -13,74</t>
+          <t>-36,53; -12,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-64,74; -24,65</t>
+          <t>-65,47; -25,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-40,59; -17,35</t>
+          <t>-40,97; -17,68</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,89; -10,38</t>
+          <t>-53,01; -13,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,84; -23,58</t>
+          <t>-76,86; -22,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-45,76; -13,17</t>
+          <t>-47,81; -13,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,03; -6,83</t>
+          <t>-37,75; -8,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,73; -17,08</t>
+          <t>-68,41; -16,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,06; -13,7</t>
+          <t>-45,43; -10,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,9; -13,74</t>
+          <t>-36,53; -12,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-64,74; -24,65</t>
+          <t>-65,47; -25,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-40,59; -17,35</t>
+          <t>-40,97; -17,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-37,7; -8,6</t>
+          <t>-37,97; -6,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-61,95; -28,92</t>
+          <t>-61,29; -28,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-72,74; -22,77</t>
+          <t>-73,95; -25,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-55,96; -17,35</t>
+          <t>-55,29; -15,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-56,64; -23,66</t>
+          <t>-58,1; -25,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-59,83; -8,31</t>
+          <t>-62,51; -7,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-39,98; -15,0</t>
+          <t>-38,16; -14,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-53,18; -31,37</t>
+          <t>-54,95; -30,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-60,53; -21,89</t>
+          <t>-59,03; -22,28</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,7; -8,6</t>
+          <t>-37,97; -6,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,95; -28,92</t>
+          <t>-61,29; -28,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-72,74; -22,77</t>
+          <t>-73,95; -25,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,96; -17,35</t>
+          <t>-55,29; -15,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,64; -23,66</t>
+          <t>-58,1; -25,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,83; -8,31</t>
+          <t>-62,51; -7,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,98; -15,0</t>
+          <t>-38,16; -14,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,18; -31,37</t>
+          <t>-54,95; -30,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,53; -21,89</t>
+          <t>-59,03; -22,28</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-41,55; -4,58</t>
+          <t>-40,61; -4,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-47,4; 0,0</t>
+          <t>-47,74; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-55,99; -11,79</t>
+          <t>-55,33; -10,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-44,74; -5,24</t>
+          <t>-45,02; -5,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-67,33; 0,0</t>
+          <t>-68,33; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-82,63; -30,84</t>
+          <t>-80,54; -30,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-33,86; -8,17</t>
+          <t>-34,56; -8,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-43,83; -4,99</t>
+          <t>-46,08; -5,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-65,69; -27,0</t>
+          <t>-64,84; -25,64</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-41,55; -4,58</t>
+          <t>-40,61; -4,53</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,4; 0,0</t>
+          <t>-47,74; 0,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-55,99; -11,79</t>
+          <t>-55,33; -10,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,74; -5,24</t>
+          <t>-45,02; -5,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,33; 0,0</t>
+          <t>-68,33; 0,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-82,63; -30,84</t>
+          <t>-80,54; -30,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,86; -8,17</t>
+          <t>-34,56; -8,47</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,83; -4,99</t>
+          <t>-46,08; -5,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-65,69; -27,0</t>
+          <t>-64,84; -25,64</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-69,9; -18,55</t>
+          <t>-69,95; -21,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-76,63; -20,71</t>
+          <t>-70,59; -15,64</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-70,07; -15,8</t>
+          <t>-69,31; -13,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-63,4; -24,78</t>
+          <t>-63,49; -24,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-90,83; -31,21</t>
+          <t>-90,64; -29,79</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-46,64; -8,74</t>
+          <t>-46,65; -10,03</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-58,47; -28,07</t>
+          <t>-58,67; -28,04</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-72,01; -34,9</t>
+          <t>-74,11; -33,68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-46,71; -17,01</t>
+          <t>-46,25; -15,84</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-69,9; -18,55</t>
+          <t>-69,95; -21,1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-76,63; -20,71</t>
+          <t>-70,59; -15,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-70,07; -15,8</t>
+          <t>-69,31; -13,85</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,4; -24,78</t>
+          <t>-63,49; -24,37</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-90,83; -31,21</t>
+          <t>-90,64; -29,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-46,64; -8,74</t>
+          <t>-46,65; -10,03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-58,47; -28,07</t>
+          <t>-58,67; -28,04</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-72,01; -34,9</t>
+          <t>-74,11; -33,68</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-46,71; -17,01</t>
+          <t>-46,25; -15,84</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-55,81; -25,03</t>
+          <t>-54,81; -23,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-56,79; -14,9</t>
+          <t>-55,73; -15,19</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-64,09; -33,14</t>
+          <t>-63,78; -32,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-60,73; -28,8</t>
+          <t>-59,67; -28,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-50,62; -6,32</t>
+          <t>-55,76; -6,19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-64,1; -32,12</t>
+          <t>-63,27; -30,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-52,3; -29,25</t>
+          <t>-53,77; -30,48</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-45,51; -16,13</t>
+          <t>-44,4; -15,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-59,6; -36,27</t>
+          <t>-59,09; -36,37</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-55,81; -25,03</t>
+          <t>-54,81; -23,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-56,79; -14,9</t>
+          <t>-55,73; -15,19</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-64,09; -33,14</t>
+          <t>-63,78; -32,92</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-60,73; -28,8</t>
+          <t>-59,67; -28,71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,62; -6,32</t>
+          <t>-55,76; -6,19</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-64,1; -32,12</t>
+          <t>-63,27; -30,08</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-52,3; -29,25</t>
+          <t>-53,77; -30,48</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-45,51; -16,13</t>
+          <t>-44,4; -15,75</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-59,6; -36,27</t>
+          <t>-59,09; -36,37</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-64,73; -30,66</t>
+          <t>-64,55; -31,08</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-63,98; -28,27</t>
+          <t>-60,44; -27,96</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-64,95; -11,92</t>
+          <t>-66,34; -12,85</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-64,36; -28,85</t>
+          <t>-62,9; -27,82</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-72,41; -42,46</t>
+          <t>-71,83; -39,73</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-64,85; -16,37</t>
+          <t>-68,77; -16,57</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-58,79; -34,84</t>
+          <t>-60,8; -35,16</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-62,38; -39,13</t>
+          <t>-63,09; -40,77</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-58,17; -21,38</t>
+          <t>-57,1; -20,22</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-64,73; -30,66</t>
+          <t>-64,55; -31,08</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-63,98; -28,27</t>
+          <t>-60,44; -27,96</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-64,95; -11,92</t>
+          <t>-66,34; -12,85</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-64,36; -28,85</t>
+          <t>-62,9; -27,82</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-72,41; -42,46</t>
+          <t>-71,83; -39,73</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-64,85; -16,37</t>
+          <t>-68,77; -16,57</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-58,79; -34,84</t>
+          <t>-60,8; -35,16</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-62,38; -39,13</t>
+          <t>-63,09; -40,77</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-58,17; -21,38</t>
+          <t>-57,1; -20,22</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-39,3; -26,63</t>
+          <t>-39,58; -27,1</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-46,55; -32,0</t>
+          <t>-45,72; -31,55</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-51,3; -23,97</t>
+          <t>-52,04; -25,12</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-44,12; -31,68</t>
+          <t>-43,61; -31,13</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-52,45; -37,17</t>
+          <t>-52,05; -37,33</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -33,48</t>
+          <t>-48,01; -34,16</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-39,59; -30,87</t>
+          <t>-39,75; -30,8</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-46,92; -36,87</t>
+          <t>-46,5; -36,81</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-47,14; -31,58</t>
+          <t>-47,48; -32,13</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-39,3; -26,63</t>
+          <t>-39,58; -27,1</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-46,55; -32,0</t>
+          <t>-45,72; -31,55</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-51,3; -23,97</t>
+          <t>-52,04; -25,12</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-44,12; -31,68</t>
+          <t>-43,61; -31,13</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-52,45; -37,17</t>
+          <t>-52,05; -37,33</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -33,48</t>
+          <t>-48,01; -34,16</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-39,59; -30,87</t>
+          <t>-39,75; -30,8</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-46,92; -36,87</t>
+          <t>-46,5; -36,81</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-47,14; -31,58</t>
+          <t>-47,48; -32,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-35,43; -6,42</t>
+          <t>-35,63; -6,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-72,86; -30,54</t>
+          <t>-72,66; -31,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-80,46; -43,05</t>
+          <t>-82,23; -43,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-66,82; -27,42</t>
+          <t>-66,54; -26,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-62,08; -22,8</t>
+          <t>-58,96; -22,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,92; -26,82</t>
+          <t>-63,89; -25,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,24; -20,26</t>
+          <t>-47,46; -20,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-59,61; -31,74</t>
+          <t>-58,81; -32,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-69,19; -40,37</t>
+          <t>-72,29; -40,43</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,43; -6,42</t>
+          <t>-35,63; -6,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,86; -30,54</t>
+          <t>-72,66; -31,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-80,46; -43,05</t>
+          <t>-82,23; -43,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,82; -27,42</t>
+          <t>-66,54; -26,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,08; -22,8</t>
+          <t>-58,96; -22,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,92; -26,82</t>
+          <t>-63,89; -25,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,24; -20,26</t>
+          <t>-47,46; -20,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,61; -31,74</t>
+          <t>-58,81; -32,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,19; -40,37</t>
+          <t>-72,29; -40,43</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-58,56; -26,28</t>
+          <t>-57,52; -24,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-41,82; -14,2</t>
+          <t>-43,19; -14,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-62,11; -9,55</t>
+          <t>-63,34; -10,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-55,09; -23,69</t>
+          <t>-56,67; -23,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-66,4; -32,63</t>
+          <t>-68,86; -32,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,12; -32,34</t>
+          <t>-57,18; -31,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,64; -29,38</t>
+          <t>-52,12; -30,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,76; -24,96</t>
+          <t>-46,85; -23,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-53,05; -17,17</t>
+          <t>-52,72; -18,31</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,56; -26,28</t>
+          <t>-57,52; -24,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,82; -14,2</t>
+          <t>-43,19; -14,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,11; -9,55</t>
+          <t>-63,34; -10,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,09; -23,69</t>
+          <t>-56,67; -23,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,4; -32,63</t>
+          <t>-68,86; -32,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,12; -32,34</t>
+          <t>-57,18; -31,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,64; -29,38</t>
+          <t>-52,12; -30,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,76; -24,96</t>
+          <t>-46,85; -23,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,05; -17,17</t>
+          <t>-52,72; -18,31</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-53,01; -13,53</t>
+          <t>-50,16; -10,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-76,86; -22,72</t>
+          <t>-76,98; -23,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-47,81; -13,78</t>
+          <t>-46,75; -12,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-37,75; -8,69</t>
+          <t>-40,18; -9,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,41; -16,93</t>
+          <t>-68,17; -16,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,43; -10,93</t>
+          <t>-45,57; -12,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,53; -12,99</t>
+          <t>-36,18; -13,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-65,47; -25,03</t>
+          <t>-65,92; -25,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-40,97; -17,68</t>
+          <t>-40,84; -16,01</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,01; -13,53</t>
+          <t>-50,16; -10,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,86; -22,72</t>
+          <t>-76,98; -23,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,81; -13,78</t>
+          <t>-46,75; -12,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,75; -8,69</t>
+          <t>-40,18; -9,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,41; -16,93</t>
+          <t>-68,17; -16,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,43; -10,93</t>
+          <t>-45,57; -12,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,53; -12,99</t>
+          <t>-36,18; -13,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,47; -25,03</t>
+          <t>-65,92; -25,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-40,97; -17,68</t>
+          <t>-40,84; -16,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-37,97; -6,43</t>
+          <t>-37,9; -7,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-61,29; -28,97</t>
+          <t>-62,07; -28,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-73,95; -25,9</t>
+          <t>-73,73; -22,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-55,29; -15,1</t>
+          <t>-56,35; -15,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,1; -25,29</t>
+          <t>-57,76; -25,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-62,51; -7,74</t>
+          <t>-59,49; -8,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-38,16; -14,54</t>
+          <t>-38,97; -15,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-54,95; -30,65</t>
+          <t>-53,97; -31,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-59,03; -22,28</t>
+          <t>-58,66; -22,29</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,97; -6,43</t>
+          <t>-37,9; -7,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,29; -28,97</t>
+          <t>-62,07; -28,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-73,95; -25,9</t>
+          <t>-73,73; -22,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,29; -15,1</t>
+          <t>-56,35; -15,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,1; -25,29</t>
+          <t>-57,76; -25,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,51; -7,74</t>
+          <t>-59,49; -8,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,16; -14,54</t>
+          <t>-38,97; -15,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,95; -30,65</t>
+          <t>-53,97; -31,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,03; -22,28</t>
+          <t>-58,66; -22,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-40,61; -4,53</t>
+          <t>-37,72; -4,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 0,0</t>
+          <t>-49,03; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-55,33; -10,42</t>
+          <t>-57,01; -10,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-45,02; -5,33</t>
+          <t>-45,61; -5,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-68,33; 0,0</t>
+          <t>-67,62; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-80,54; -30,16</t>
+          <t>-79,94; -28,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-34,56; -8,47</t>
+          <t>-33,63; -8,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-46,08; -5,3</t>
+          <t>-46,33; -5,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-64,84; -25,64</t>
+          <t>-66,47; -25,34</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-40,61; -4,53</t>
+          <t>-37,72; -4,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 0,0</t>
+          <t>-49,03; 0,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-55,33; -10,42</t>
+          <t>-57,01; -10,94</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,02; -5,33</t>
+          <t>-45,61; -5,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-68,33; 0,0</t>
+          <t>-67,62; 0,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-80,54; -30,16</t>
+          <t>-79,94; -28,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,56; -8,47</t>
+          <t>-33,63; -8,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,08; -5,3</t>
+          <t>-46,33; -5,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-64,84; -25,64</t>
+          <t>-66,47; -25,34</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-69,95; -21,1</t>
+          <t>-68,72; -18,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-70,59; -15,64</t>
+          <t>-70,41; -16,07</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-69,31; -13,85</t>
+          <t>-69,56; -15,67</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-63,49; -24,37</t>
+          <t>-63,11; -24,51</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-90,64; -29,79</t>
+          <t>-84,77; -27,56</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-46,65; -10,03</t>
+          <t>-46,54; -10,07</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-58,67; -28,04</t>
+          <t>-57,35; -28,33</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-74,11; -33,68</t>
+          <t>-73,75; -32,92</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-46,25; -15,84</t>
+          <t>-46,25; -15,87</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-69,95; -21,1</t>
+          <t>-68,72; -18,66</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-70,59; -15,64</t>
+          <t>-70,41; -16,07</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-69,31; -13,85</t>
+          <t>-69,56; -15,67</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,49; -24,37</t>
+          <t>-63,11; -24,51</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-90,64; -29,79</t>
+          <t>-84,77; -27,56</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-46,65; -10,03</t>
+          <t>-46,54; -10,07</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-58,67; -28,04</t>
+          <t>-57,35; -28,33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-74,11; -33,68</t>
+          <t>-73,75; -32,92</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-46,25; -15,84</t>
+          <t>-46,25; -15,87</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-54,81; -23,78</t>
+          <t>-55,79; -25,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-55,73; -15,19</t>
+          <t>-55,57; -14,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-63,78; -32,92</t>
+          <t>-63,11; -33,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-59,67; -28,71</t>
+          <t>-60,04; -28,26</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-55,76; -6,19</t>
+          <t>-51,42; -6,58</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-63,27; -30,08</t>
+          <t>-62,48; -31,73</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-53,77; -30,48</t>
+          <t>-53,37; -31,0</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-44,4; -15,75</t>
+          <t>-46,38; -16,28</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-59,09; -36,37</t>
+          <t>-59,94; -36,82</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-54,81; -23,78</t>
+          <t>-55,79; -25,0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-55,73; -15,19</t>
+          <t>-55,57; -14,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-63,78; -32,92</t>
+          <t>-63,11; -33,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-59,67; -28,71</t>
+          <t>-60,04; -28,26</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-55,76; -6,19</t>
+          <t>-51,42; -6,58</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-63,27; -30,08</t>
+          <t>-62,48; -31,73</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-53,77; -30,48</t>
+          <t>-53,37; -31,0</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-44,4; -15,75</t>
+          <t>-46,38; -16,28</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-59,09; -36,37</t>
+          <t>-59,94; -36,82</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-64,55; -31,08</t>
+          <t>-65,85; -28,7</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-60,44; -27,96</t>
+          <t>-63,1; -28,36</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-66,34; -12,85</t>
+          <t>-66,16; -12,66</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-62,9; -27,82</t>
+          <t>-64,86; -28,7</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-71,83; -39,73</t>
+          <t>-71,33; -40,26</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-68,77; -16,57</t>
+          <t>-65,98; -14,73</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-60,8; -35,16</t>
+          <t>-59,12; -33,65</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-63,09; -40,77</t>
+          <t>-62,53; -39,4</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-57,1; -20,22</t>
+          <t>-59,06; -22,68</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-64,55; -31,08</t>
+          <t>-65,85; -28,7</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-60,44; -27,96</t>
+          <t>-63,1; -28,36</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-66,34; -12,85</t>
+          <t>-66,16; -12,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-62,9; -27,82</t>
+          <t>-64,86; -28,7</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-71,83; -39,73</t>
+          <t>-71,33; -40,26</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-68,77; -16,57</t>
+          <t>-65,98; -14,73</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-60,8; -35,16</t>
+          <t>-59,12; -33,65</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-63,09; -40,77</t>
+          <t>-62,53; -39,4</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-57,1; -20,22</t>
+          <t>-59,06; -22,68</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-39,58; -27,1</t>
+          <t>-38,83; -26,1</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-45,72; -31,55</t>
+          <t>-46,26; -31,83</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-52,04; -25,12</t>
+          <t>-51,72; -25,75</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-43,61; -31,13</t>
+          <t>-43,93; -30,9</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -37,33</t>
+          <t>-52,22; -37,65</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -34,16</t>
+          <t>-47,82; -34,11</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-39,75; -30,8</t>
+          <t>-40,34; -30,98</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-46,5; -36,81</t>
+          <t>-47,15; -37,11</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-47,48; -32,13</t>
+          <t>-46,8; -32,27</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-39,58; -27,1</t>
+          <t>-38,83; -26,1</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-45,72; -31,55</t>
+          <t>-46,26; -31,83</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-52,04; -25,12</t>
+          <t>-51,72; -25,75</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-43,61; -31,13</t>
+          <t>-43,93; -30,9</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -37,33</t>
+          <t>-52,22; -37,65</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -34,16</t>
+          <t>-47,82; -34,11</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-39,75; -30,8</t>
+          <t>-40,34; -30,98</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-46,5; -36,81</t>
+          <t>-47,15; -37,11</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-47,48; -32,13</t>
+          <t>-46,8; -32,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-47,07</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-39,79</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-42,81</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-17,11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-51,46</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-61,84</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-47,07</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-39,79</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-44,14</t>
+          <t>-48,13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-54,34</t>
+          <t>-45,57</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-35,63; -6,12</t>
+          <t>-65,95; -27,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-72,66; -31,47</t>
+          <t>-58,79; -23,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-82,23; -43,92</t>
+          <t>-61,89; -25,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-66,54; -26,89</t>
+          <t>-33,59; -6,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,96; -22,4</t>
+          <t>-71,73; -29,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,89; -25,97</t>
+          <t>-66,59; -32,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,46; -20,58</t>
+          <t>-48,75; -21,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-58,81; -32,46</t>
+          <t>-59,31; -30,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-72,29; -40,43</t>
+          <t>-57,76; -32,46</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-47,07%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-39,79%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-42,81%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-17,11%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-51,46%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-61,84%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-47,07%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-39,79%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-44,14%</t>
+          <t>-48,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-54,34%</t>
+          <t>-45,57%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,63; -6,12</t>
+          <t>-65,95; -27,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,66; -31,47</t>
+          <t>-58,79; -23,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,23; -43,92</t>
+          <t>-61,89; -25,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,54; -26,89</t>
+          <t>-33,59; -6,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,96; -22,4</t>
+          <t>-71,73; -29,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,89; -25,97</t>
+          <t>-66,59; -32,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,46; -20,58</t>
+          <t>-48,75; -21,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,81; -32,46</t>
+          <t>-59,31; -30,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,29; -40,43</t>
+          <t>-57,76; -32,46</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-39,88</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-48,47</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-44,29</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-40,84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-25,98</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-32,88</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-39,88</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-48,47</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-44,44</t>
+          <t>-54,04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-37,89</t>
+          <t>-48,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-57,52; -24,37</t>
+          <t>-55,6; -24,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-43,19; -14,62</t>
+          <t>-67,53; -31,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-63,34; -10,53</t>
+          <t>-57,66; -31,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,67; -23,86</t>
+          <t>-58,02; -26,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-68,86; -32,61</t>
+          <t>-43,55; -12,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,18; -31,96</t>
+          <t>-69,49; -38,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,12; -30,74</t>
+          <t>-52,07; -29,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,85; -23,86</t>
+          <t>-46,96; -25,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-52,72; -18,31</t>
+          <t>-57,75; -38,36</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-39,88%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-48,47%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-44,29%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-40,84%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-25,98%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-32,88%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-39,88%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-48,47%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-44,44%</t>
+          <t>-54,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-37,89%</t>
+          <t>-48,93%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,52; -24,37</t>
+          <t>-55,6; -24,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,19; -14,62</t>
+          <t>-67,53; -31,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,34; -10,53</t>
+          <t>-57,66; -31,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,67; -23,86</t>
+          <t>-58,02; -26,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,86; -32,61</t>
+          <t>-43,55; -12,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,18; -31,96</t>
+          <t>-69,49; -38,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,12; -30,74</t>
+          <t>-52,07; -29,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,85; -23,86</t>
+          <t>-46,96; -25,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,72; -18,31</t>
+          <t>-57,75; -38,36</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-20,39</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-42,41</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-27,91</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-29,26</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-47,28</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-27,86</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-20,39</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-42,41</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-27,68</t>
+          <t>-26,42</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-27,76</t>
+          <t>-27,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-50,16; -10,28</t>
+          <t>-37,03; -6,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-76,98; -23,58</t>
+          <t>-68,73; -17,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-46,75; -12,9</t>
+          <t>-47,56; -13,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-40,18; -9,49</t>
+          <t>-52,89; -10,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,17; -16,79</t>
+          <t>-76,84; -23,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,57; -12,92</t>
+          <t>-44,45; -12,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,18; -13,49</t>
+          <t>-36,9; -13,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-65,92; -25,06</t>
+          <t>-64,74; -24,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-40,84; -16,01</t>
+          <t>-40,09; -17,08</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-20,39%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-42,41%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-27,91%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-29,26%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-47,28%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-27,86%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-20,39%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-42,41%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,68%</t>
+          <t>-26,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-27,76%</t>
+          <t>-27,18%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,16; -10,28</t>
+          <t>-37,03; -6,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,98; -23,58</t>
+          <t>-68,73; -17,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,75; -12,9</t>
+          <t>-47,56; -13,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,18; -9,49</t>
+          <t>-52,89; -10,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,17; -16,79</t>
+          <t>-76,84; -23,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,57; -12,92</t>
+          <t>-44,45; -12,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,18; -13,49</t>
+          <t>-36,9; -13,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,92; -25,06</t>
+          <t>-64,74; -24,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-40,84; -16,01</t>
+          <t>-40,09; -17,08</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-33,18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-40,29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-29,89</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-19,65</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-44,99</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-50,02</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-33,18</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-40,29</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-28,0</t>
+          <t>-49,04</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-39,69</t>
+          <t>-40,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-37,9; -7,26</t>
+          <t>-55,96; -17,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-62,07; -28,74</t>
+          <t>-56,64; -23,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-73,73; -22,83</t>
+          <t>-62,17; -9,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-56,35; -15,88</t>
+          <t>-37,7; -8,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-57,76; -25,34</t>
+          <t>-61,95; -28,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-59,49; -8,39</t>
+          <t>-73,3; -23,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-38,97; -15,32</t>
+          <t>-39,98; -15,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-53,97; -31,39</t>
+          <t>-53,18; -31,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-58,66; -22,29</t>
+          <t>-61,63; -23,26</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-33,18%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-40,29%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-29,89%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-19,65%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-44,99%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-50,02%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-33,18%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-40,29%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-28,0%</t>
+          <t>-49,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-39,69%</t>
+          <t>-40,23%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,9; -7,26</t>
+          <t>-55,96; -17,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-62,07; -28,74</t>
+          <t>-56,64; -23,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-73,73; -22,83</t>
+          <t>-62,17; -9,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,35; -15,88</t>
+          <t>-37,7; -8,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,76; -25,34</t>
+          <t>-61,95; -28,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,49; -8,39</t>
+          <t>-73,3; -23,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,97; -15,32</t>
+          <t>-39,98; -15,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,97; -31,39</t>
+          <t>-53,18; -31,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,66; -22,29</t>
+          <t>-61,63; -23,26</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-21,38</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-27,3</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-52,8</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-15,75</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-11,84</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-29,46</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-21,38</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-27,3</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-57,24</t>
+          <t>-29,19</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-45,15</t>
+          <t>-41,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-37,72; -4,46</t>
+          <t>-44,74; -5,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-49,03; 0,0</t>
+          <t>-67,33; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-57,01; -10,94</t>
+          <t>-80,52; -27,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-45,61; -5,26</t>
+          <t>-41,55; -4,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-67,62; 0,0</t>
+          <t>-47,4; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-79,94; -28,73</t>
+          <t>-55,64; -12,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-33,63; -8,16</t>
+          <t>-33,86; -8,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-46,33; -5,4</t>
+          <t>-43,83; -4,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-66,47; -25,34</t>
+          <t>-62,95; -24,68</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-21,38%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-27,3%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-52,8%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-15,75%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-11,84%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-29,46%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-21,38%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-27,3%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-57,24%</t>
+          <t>-29,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-45,15%</t>
+          <t>-41,84%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-37,72; -4,46</t>
+          <t>-44,74; -5,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,03; 0,0</t>
+          <t>-67,33; 0,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,01; -10,94</t>
+          <t>-80,52; -27,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,61; -5,26</t>
+          <t>-41,55; -4,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,62; 0,0</t>
+          <t>-47,4; 0,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-79,94; -28,73</t>
+          <t>-55,64; -12,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,63; -8,16</t>
+          <t>-33,86; -8,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,33; -5,4</t>
+          <t>-43,83; -4,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-66,47; -25,34</t>
+          <t>-62,95; -24,68</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-42,82</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-63,53</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-25,79</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-44,11</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-44,74</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-39,59</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-42,82</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-63,53</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-23,96</t>
+          <t>-41,47</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-29,6</t>
+          <t>-32,08</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-68,72; -18,66</t>
+          <t>-63,4; -24,78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-70,41; -16,07</t>
+          <t>-90,83; -31,21</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-69,56; -15,67</t>
+          <t>-49,66; -9,41</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-63,11; -24,51</t>
+          <t>-69,9; -18,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-84,77; -27,56</t>
+          <t>-76,63; -20,71</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-46,54; -10,07</t>
+          <t>-71,28; -16,89</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-57,35; -28,33</t>
+          <t>-58,47; -28,07</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-73,75; -32,92</t>
+          <t>-72,01; -34,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-46,25; -15,87</t>
+          <t>-50,23; -18,84</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-42,82%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-63,53%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-25,79%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-44,11%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-44,74%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-39,59%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-42,82%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-63,53%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-23,96%</t>
+          <t>-41,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-29,6%</t>
+          <t>-32,08%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-68,72; -18,66</t>
+          <t>-63,4; -24,78</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-70,41; -16,07</t>
+          <t>-90,83; -31,21</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-69,56; -15,67</t>
+          <t>-49,66; -9,41</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,11; -24,51</t>
+          <t>-69,9; -18,55</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-84,77; -27,56</t>
+          <t>-76,63; -20,71</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-46,54; -10,07</t>
+          <t>-71,28; -16,89</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-57,35; -28,33</t>
+          <t>-58,47; -28,07</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-73,75; -32,92</t>
+          <t>-72,01; -34,9</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-46,25; -15,87</t>
+          <t>-50,23; -18,84</t>
         </is>
       </c>
     </row>
@@ -1920,47 +1920,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-43,74</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-25,05</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-44,34</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-39,38</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-33,06</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-48,48</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-43,74</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-25,05</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>-49,17</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-41,51</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-29,65</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>-46,36</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-41,51</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-29,65</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>-47,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-55,79; -25,0</t>
+          <t>-60,73; -28,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-55,57; -14,45</t>
+          <t>-50,62; -6,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-63,11; -33,57</t>
+          <t>-62,51; -29,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-60,04; -28,26</t>
+          <t>-55,81; -25,03</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-51,42; -6,58</t>
+          <t>-56,79; -14,9</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-62,48; -31,73</t>
+          <t>-64,83; -33,29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-53,37; -31,0</t>
+          <t>-52,3; -29,25</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-46,38; -16,28</t>
+          <t>-45,51; -16,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-59,94; -36,82</t>
+          <t>-59,62; -35,64</t>
         </is>
       </c>
     </row>
@@ -2026,47 +2026,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-43,74%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-25,05%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-44,34%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-39,38%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-33,06%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-48,48%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-43,74%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-25,05%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>-49,17%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-41,51%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-29,65%</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
           <t>-46,36%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-41,51%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-29,65%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>-47,21%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-55,79; -25,0</t>
+          <t>-60,73; -28,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-55,57; -14,45</t>
+          <t>-50,62; -6,32</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-63,11; -33,57</t>
+          <t>-62,51; -29,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-60,04; -28,26</t>
+          <t>-55,81; -25,03</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-51,42; -6,58</t>
+          <t>-56,79; -14,9</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-62,48; -31,73</t>
+          <t>-64,83; -33,29</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-53,37; -31,0</t>
+          <t>-52,3; -29,25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-46,38; -16,28</t>
+          <t>-45,51; -16,13</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-59,94; -36,82</t>
+          <t>-59,62; -35,64</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-45,32</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-56,78</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-41,55</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-47,6</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-43,59</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-37,06</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-45,32</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-56,78</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-40,36</t>
+          <t>-39,2</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-39,01</t>
+          <t>-40,63</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-65,85; -28,7</t>
+          <t>-64,36; -28,85</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-63,1; -28,36</t>
+          <t>-72,41; -42,46</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-66,16; -12,66</t>
+          <t>-66,55; -18,05</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-64,86; -28,7</t>
+          <t>-64,73; -30,66</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-71,33; -40,26</t>
+          <t>-63,98; -28,27</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-65,98; -14,73</t>
+          <t>-67,87; -11,68</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-59,12; -33,65</t>
+          <t>-58,79; -34,84</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-62,53; -39,4</t>
+          <t>-62,38; -39,13</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-59,06; -22,68</t>
+          <t>-60,33; -22,0</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-45,32%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-56,78%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-41,55%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-47,6%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-43,59%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-37,06%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-45,32%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-56,78%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-40,36%</t>
+          <t>-39,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-39,01%</t>
+          <t>-40,63%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-65,85; -28,7</t>
+          <t>-64,36; -28,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-63,1; -28,36</t>
+          <t>-72,41; -42,46</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-66,16; -12,66</t>
+          <t>-66,55; -18,05</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-64,86; -28,7</t>
+          <t>-64,73; -30,66</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-71,33; -40,26</t>
+          <t>-63,98; -28,27</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-65,98; -14,73</t>
+          <t>-67,87; -11,68</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-59,12; -33,65</t>
+          <t>-58,79; -34,84</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-62,53; -39,4</t>
+          <t>-62,38; -39,13</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-59,06; -22,68</t>
+          <t>-60,33; -22,0</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-37,6</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-44,86</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-40,49</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-32,77</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-38,64</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-41,47</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-37,6</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-44,86</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-40,97</t>
+          <t>-45,47</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-41,21</t>
+          <t>-42,8</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-38,83; -26,1</t>
+          <t>-44,12; -31,68</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-46,26; -31,83</t>
+          <t>-52,45; -37,17</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-51,72; -25,75</t>
+          <t>-46,67; -33,11</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-43,93; -30,9</t>
+          <t>-39,3; -26,63</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-52,22; -37,65</t>
+          <t>-46,55; -32,0</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-47,82; -34,11</t>
+          <t>-52,8; -38,91</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-40,34; -30,98</t>
+          <t>-39,59; -30,87</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-47,15; -37,11</t>
+          <t>-46,92; -36,87</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-46,8; -32,27</t>
+          <t>-47,6; -38,07</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-37,6%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-44,86%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-40,49%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-32,77%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-38,64%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-41,47%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-37,6%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-44,86%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-40,97%</t>
+          <t>-45,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-41,21%</t>
+          <t>-42,8%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-38,83; -26,1</t>
+          <t>-44,12; -31,68</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-46,26; -31,83</t>
+          <t>-52,45; -37,17</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-51,72; -25,75</t>
+          <t>-46,67; -33,11</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-43,93; -30,9</t>
+          <t>-39,3; -26,63</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-52,22; -37,65</t>
+          <t>-46,55; -32,0</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-47,82; -34,11</t>
+          <t>-52,8; -38,91</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-40,34; -30,98</t>
+          <t>-39,59; -30,87</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-47,15; -37,11</t>
+          <t>-46,92; -36,87</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-46,8; -32,27</t>
+          <t>-47,6; -38,07</t>
         </is>
       </c>
     </row>
